--- a/reports/二级子公司D_利润表_2025-02.xlsx
+++ b/reports/二级子公司D_利润表_2025-02.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>73362673</v>
+        <v>74313786</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>71743584</v>
+        <v>71089188</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>142915122</v>
+        <v>142182306</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>246874</v>
+        <v>247099</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>492820</v>
+        <v>492986</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>210418</v>
+        <v>212205</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>422385</v>
+        <v>423492</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>176890</v>
+        <v>177027</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>352008</v>
+        <v>353525</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>157475</v>
+        <v>159333</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>316797</v>
+        <v>318486</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>88525</v>
+        <v>88432</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>175999</v>
+        <v>176946</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>70019</v>
+        <v>70616</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>140803</v>
+        <v>141431</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>72412472</v>
+        <v>73359074</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>70793383</v>
+        <v>70134476</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>3962638</v>
+        <v>3944118</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>7919651</v>
+        <v>7906838</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>308415</v>
+        <v>306310</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>616026</v>
+        <v>613750</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>526305</v>
+        <v>524832</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>1055961</v>
+        <v>1050718</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>63658411</v>
+        <v>63014321</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>126723513</v>
+        <v>126026833</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1050006</v>
+        <v>1051827</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2111969</v>
+        <v>2101491</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>354112</v>
+        <v>351383</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>704000</v>
+        <v>701461</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1750065</v>
+        <v>1761330</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>3520052</v>
+        <v>3514363</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>442047</v>
+        <v>441377</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>879976</v>
+        <v>880602</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1579039</v>
+        <v>1591848</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>3168119</v>
+        <v>3177030</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>40050</v>
+        <v>40236</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>79996</v>
+        <v>80361</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>955931</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>1911035</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>636583</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>1273924</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>48275055</v>
+        <v>51350466</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>43279755</v>
+        <v>42937992</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>42492364</v>
+        <v>42149362</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>84480372</v>
+        <v>84506639</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>787391</v>
+        <v>788630</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>1584017</v>
+        <v>1580908</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1575105</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>3155720</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>503845</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>1008571</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>315119</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>630141</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>378757</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>756640</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>284713</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>568319</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>190287</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>379664</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>158941</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>317114</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>752405</v>
+        <v>751842</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>1496013</v>
+        <v>1500650</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>568604</v>
+        <v>575407</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>1144007</v>
+        <v>1149355</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>442337</v>
+        <v>442520</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>879982</v>
+        <v>884778</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3330338</v>
+        <v>3359019</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>6688215</v>
+        <v>6722934</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>150360</v>
+        <v>132325</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>299988</v>
+        <v>265081</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>319860</v>
+        <v>320001</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>640028</v>
+        <v>641440</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>359434</v>
+        <v>320001</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>719969</v>
+        <v>641440</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>40136</v>
+        <v>39821</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>80003</v>
+        <v>79822</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>161072</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>322675</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>275549</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>551507</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>107445</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>214827</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>80723</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>161240</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>134852</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>269157</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>396562</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>791205</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>72265</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>144185</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>54286</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>108362</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>90539</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>180870</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>63354</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>126688</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>45192</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>90461</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>36078</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>72280</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>26991</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>54106</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>24137417</v>
+        <v>23022976</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>27772465</v>
+        <v>25635690</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>157479</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>315443</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>44734</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>89523</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>70165</v>
+        <v>69653</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>140006</v>
+        <v>139246</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>24067252</v>
+        <v>23110802</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2513222</v>
+        <v>2498092</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>5000106</v>
+        <v>4985682</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>21554030</v>
+        <v>20612710</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>21554030</v>
+        <v>20612710</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>21554030</v>
+        <v>20612710</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>21554030</v>
+        <v>20612710</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>21554030</v>
+        <v>20612710</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
